--- a/EndResult/200m Bryst.xlsx
+++ b/EndResult/200m Bryst.xlsx
@@ -646,20 +646,20 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Johan Hjelseth Storstad</t>
+          <t>Gabriel Rognes Steen</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2.27,79</t>
+          <t>2.27,55</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>18.04.2021</t>
+          <t>25.01.2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -681,25 +681,25 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Tobias Gilbu</t>
+          <t>Johan Hjelseth Storstad</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2.28,16</t>
+          <t>2.27,79</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>31.10.2020</t>
+          <t>18.04.2021</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Stavanger</t>
+          <t>Trondheim</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -716,25 +716,25 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Manith Randula Attanapola</t>
+          <t>Tobias Gilbu</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2.28,31</t>
+          <t>2.28,16</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>21.03.2015</t>
+          <t>31.10.2020</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kristiansand</t>
+          <t>Stavanger</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -751,25 +751,25 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Scott Rene Høgenhaug</t>
+          <t>Manith Randula Attanapola</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2.30,56</t>
+          <t>2.28,31</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>508</v>
+        <v>531</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>21.01.2018</t>
+          <t>21.03.2015</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Trondheim</t>
+          <t>Kristiansand</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -786,25 +786,25 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sebastian Amundsen</t>
+          <t>Ole Skuseth</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2.30,88</t>
+          <t>2.30,40</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>02.11.2019</t>
+          <t>14.03.2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Stavanger</t>
+          <t>Kristiansund</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1082,25 +1082,25 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Scott Rene Høgenhaug</t>
+          <t>Einar Woldseth</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2.37,56</t>
+          <t>2.36,37</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>505</v>
+        <v>516</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>28.04.2018</t>
+          <t>18.04.2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Namsos</t>
+          <t>Bergen</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1117,25 +1117,25 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Manith Randula Attanapola</t>
+          <t>Scott Rene Høgenhaug</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2.38,40</t>
+          <t>2.37,56</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>497</v>
+        <v>505</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>05.07.2015</t>
+          <t>28.04.2018</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bergen</t>
+          <t>Namsos</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1152,25 +1152,25 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Tobias Gilbu</t>
+          <t>Ole Skuseth</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2.40,03</t>
+          <t>2.38,14</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>482</v>
+        <v>499</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>01.05.2022</t>
+          <t>18.04.2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hamar</t>
+          <t>Bergen</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1187,25 +1187,25 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Simen Dahl Stensaas</t>
+          <t>Manith Randula Attanapola</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2.41,96</t>
+          <t>2.38,40</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>465</v>
+        <v>497</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>18.07.2014</t>
+          <t>05.07.2015</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Drammen</t>
+          <t>Bergen</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1989,25 +1989,25 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Annika Krill</t>
+          <t>Nicole Kulagina</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2.56,70</t>
+          <t>2.56,23</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>10.07.2005</t>
+          <t>17.04.2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hamar</t>
+          <t>Bergen</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
